--- a/data/Escenarios_DCH/Carga_on_board_fixed_3estaciones/elmo_data.xlsx
+++ b/data/Escenarios_DCH/Carga_on_board_fixed_3estaciones/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_DCH\Carga_on_board_fixed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_DCH\Carga_on_board_fixed_3estaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7217129E-A84F-411C-ABCD-45F0FE60DB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5699DCF9-2E19-4A0E-B0B6-CBF4E521D9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -3446,19 +3446,19 @@
         <v>380</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>215756</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3469,19 +3469,19 @@
         <v>388</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>215756</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3492,19 +3492,19 @@
         <v>389</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>215756</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
   </sheetData>

--- a/data/Escenarios_DCH/Carga_on_board_fixed_3estaciones/elmo_data.xlsx
+++ b/data/Escenarios_DCH/Carga_on_board_fixed_3estaciones/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_DCH\Carga_on_board_fixed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH\Carga_on_board_fixed_3estaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7217129E-A84F-411C-ABCD-45F0FE60DB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698B6125-96A9-4479-822A-FF72E05FB9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -2087,36 +2087,36 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AD17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="21" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" style="22" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="21" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="21" customWidth="1"/>
-    <col min="16" max="16" width="17.109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" style="22" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="22" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.88671875" style="22" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.88671875" style="22" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5546875" style="22" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.33203125" style="22" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.85546875" style="22" customWidth="1"/>
+    <col min="24" max="24" width="18.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>3</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="29">
         <v>1</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="29">
         <v>2</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29">
         <v>3</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29">
         <v>4</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <v>5</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29">
         <v>6</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="29">
         <v>7</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29">
         <v>8</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29">
         <v>9</v>
       </c>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AD11"/>
     </row>
-    <row r="12" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="29">
         <v>10</v>
       </c>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AD12"/>
     </row>
-    <row r="13" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29">
         <v>11</v>
       </c>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="AD13"/>
     </row>
-    <row r="14" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29">
         <v>12</v>
       </c>
@@ -3372,9 +3372,9 @@
       </c>
       <c r="AD14"/>
     </row>
-    <row r="15" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3384,15 +3384,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3446,22 +3446,22 @@
         <v>380</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>215756</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3469,22 +3469,22 @@
         <v>388</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>215756</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3492,19 +3492,19 @@
         <v>389</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>215756</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
   </sheetData>
@@ -3516,9 +3516,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3589,17 +3589,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H346"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
         <v>3</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="57">
         <v>0</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="58">
         <v>1</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58">
         <v>2</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="57">
         <v>3</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58">
         <v>4</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="58">
         <v>5</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="57">
         <v>6</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="58">
         <v>7</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58">
         <v>8</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="57">
         <v>9</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58">
         <v>10</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="58">
         <v>11</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58">
         <v>12</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="57">
         <v>13</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58">
         <v>14</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58">
         <v>15</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="57">
         <v>16</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
         <v>17</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58">
         <v>18</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="57">
         <v>19</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58">
         <v>20</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58">
         <v>21</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58">
         <v>22</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="57">
         <v>23</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58">
         <v>24</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="57">
         <v>25</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58">
         <v>26</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="58">
         <v>27</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="57">
         <v>28</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="58">
         <v>29</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58">
         <v>30</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="57">
         <v>31</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58">
         <v>32</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="58">
         <v>33</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="57">
         <v>34</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="58">
         <v>35</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
         <v>36</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58">
         <v>37</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="57">
         <v>38</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="58">
         <v>39</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="58">
         <v>40</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="58">
         <v>41</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="58">
         <v>42</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="58">
         <v>43</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="58">
         <v>44</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="58">
         <v>45</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="58">
         <v>46</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="58">
         <v>47</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="58">
         <v>48</v>
       </c>
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="58">
         <v>49</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="58">
         <v>50</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="58">
         <v>51</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="58">
         <v>52</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="58">
         <v>53</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="58">
         <v>54</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="58">
         <v>55</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="58">
         <v>56</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="58">
         <v>57</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="58">
         <v>58</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="58">
         <v>59</v>
       </c>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="58">
         <v>60</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="58">
         <v>61</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="58">
         <v>62</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="58">
         <v>63</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="58">
         <v>64</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="58">
         <v>65</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="58">
         <v>66</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="58">
         <v>67</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="58">
         <v>68</v>
       </c>
@@ -5445,7 +5445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="58">
         <v>69</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="58">
         <v>70</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="58">
         <v>71</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="58">
         <v>72</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="58">
         <v>73</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="58">
         <v>74</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="58">
         <v>75</v>
       </c>
@@ -5627,7 +5627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="58">
         <v>76</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="58">
         <v>77</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="58">
         <v>78</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="58">
         <v>79</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="58">
         <v>80</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="58">
         <v>81</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="58">
         <v>82</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="58">
         <v>83</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="58">
         <v>84</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="58">
         <v>85</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="58">
         <v>86</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="58">
         <v>87</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="58">
         <v>88</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="58">
         <v>89</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="58">
         <v>90</v>
       </c>
@@ -6017,7 +6017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="58">
         <v>91</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="58">
         <v>92</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="58">
         <v>93</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="58">
         <v>94</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="58">
         <v>95</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="58">
         <v>96</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="58">
         <v>97</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="58">
         <v>98</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="58">
         <v>99</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="58">
         <v>100</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="58">
         <v>101</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="58">
         <v>102</v>
       </c>
@@ -6329,7 +6329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="58">
         <v>103</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="58">
         <v>104</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="58">
         <v>105</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="58">
         <v>106</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="58">
         <v>107</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="58">
         <v>108</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="58">
         <v>109</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="58">
         <v>110</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="58">
         <v>111</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="58">
         <v>112</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="58">
         <v>113</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="58">
         <v>114</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="58">
         <v>115</v>
       </c>
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="58">
         <v>116</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="58">
         <v>117</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="58">
         <v>118</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="58">
         <v>119</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="58">
         <v>120</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="58">
         <v>121</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="58">
         <v>122</v>
       </c>
@@ -6849,7 +6849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="58">
         <v>123</v>
       </c>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="58">
         <v>124</v>
       </c>
@@ -6901,7 +6901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="58">
         <v>125</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="58">
         <v>126</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="58">
         <v>127</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="58">
         <v>128</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="58">
         <v>129</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="58">
         <v>130</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="58">
         <v>131</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="58">
         <v>132</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="58">
         <v>133</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="58">
         <v>134</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="58">
         <v>135</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="58">
         <v>136</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="58">
         <v>137</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="58">
         <v>138</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="58">
         <v>139</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="58">
         <v>140</v>
       </c>
@@ -7317,7 +7317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="58">
         <v>141</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="58">
         <v>142</v>
       </c>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="58">
         <v>143</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="58">
         <v>144</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="58">
         <v>145</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="58">
         <v>146</v>
       </c>
@@ -7473,7 +7473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="58">
         <v>147</v>
       </c>
@@ -7499,7 +7499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="58">
         <v>148</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="58">
         <v>149</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="58">
         <v>150</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="58">
         <v>151</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="58">
         <v>152</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="58">
         <v>153</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="58">
         <v>154</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="58">
         <v>155</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="58">
         <v>156</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="58">
         <v>157</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="58">
         <v>158</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="58">
         <v>159</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="58">
         <v>160</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="58">
         <v>161</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="58">
         <v>162</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="58">
         <v>163</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="58">
         <v>164</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="58">
         <v>165</v>
       </c>
@@ -7967,7 +7967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="58">
         <v>166</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="58">
         <v>167</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="58">
         <v>168</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="58">
         <v>169</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="58">
         <v>170</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="58">
         <v>171</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="58">
         <v>172</v>
       </c>
@@ -8149,7 +8149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="58">
         <v>173</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="58">
         <v>174</v>
       </c>
@@ -8201,7 +8201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="58">
         <v>175</v>
       </c>
@@ -8227,7 +8227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="58">
         <v>176</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="58">
         <v>177</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="58">
         <v>178</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="58">
         <v>179</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="58">
         <v>180</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="58">
         <v>181</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="58">
         <v>182</v>
       </c>
@@ -8409,7 +8409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="58">
         <v>183</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="58">
         <v>184</v>
       </c>
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="58">
         <v>185</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="58">
         <v>186</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="58">
         <v>187</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="58">
         <v>188</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="58">
         <v>189</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="58">
         <v>190</v>
       </c>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="58">
         <v>191</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="58">
         <v>192</v>
       </c>
@@ -8669,7 +8669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="58">
         <v>193</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="58">
         <v>194</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="58">
         <v>195</v>
       </c>
@@ -8747,7 +8747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="58">
         <v>196</v>
       </c>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="58">
         <v>197</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="58">
         <v>198</v>
       </c>
@@ -8825,7 +8825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="58">
         <v>199</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="58">
         <v>200</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="58">
         <v>201</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="58">
         <v>202</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="58">
         <v>203</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="58">
         <v>204</v>
       </c>
@@ -8981,7 +8981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="58">
         <v>205</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="58">
         <v>206</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="58">
         <v>207</v>
       </c>
@@ -9059,7 +9059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="58">
         <v>208</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="58">
         <v>209</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="58">
         <v>210</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="58">
         <v>211</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="58">
         <v>212</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="58">
         <v>213</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="58">
         <v>214</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="58">
         <v>215</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="58">
         <v>216</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="58">
         <v>217</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="58">
         <v>218</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="58">
         <v>219</v>
       </c>
@@ -9371,7 +9371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="58">
         <v>220</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="58">
         <v>221</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="58">
         <v>222</v>
       </c>
@@ -9449,7 +9449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="58">
         <v>223</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="58">
         <v>224</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="58">
         <v>225</v>
       </c>
@@ -9527,7 +9527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="58">
         <v>226</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="58">
         <v>227</v>
       </c>
@@ -9579,7 +9579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="58">
         <v>228</v>
       </c>
@@ -9605,7 +9605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="58">
         <v>229</v>
       </c>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="58">
         <v>230</v>
       </c>
@@ -9657,7 +9657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="58">
         <v>231</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="58">
         <v>232</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="58">
         <v>233</v>
       </c>
@@ -9735,7 +9735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="58">
         <v>234</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="58">
         <v>235</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="58">
         <v>236</v>
       </c>
@@ -9813,7 +9813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="58">
         <v>237</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="58">
         <v>238</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="58">
         <v>239</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="58">
         <v>240</v>
       </c>
@@ -9917,7 +9917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="58">
         <v>241</v>
       </c>
@@ -9943,7 +9943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="58">
         <v>242</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="58">
         <v>243</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="58">
         <v>244</v>
       </c>
@@ -10021,7 +10021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="58">
         <v>245</v>
       </c>
@@ -10047,7 +10047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="58">
         <v>246</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="58">
         <v>247</v>
       </c>
@@ -10099,7 +10099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="58">
         <v>248</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="58">
         <v>249</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="58">
         <v>250</v>
       </c>
@@ -10177,7 +10177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="58">
         <v>251</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="58">
         <v>252</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="58">
         <v>253</v>
       </c>
@@ -10255,7 +10255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="58">
         <v>254</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="58">
         <v>255</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="58">
         <v>256</v>
       </c>
@@ -10333,7 +10333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="58">
         <v>257</v>
       </c>
@@ -10359,7 +10359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="58">
         <v>258</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="58">
         <v>259</v>
       </c>
@@ -10411,7 +10411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="58">
         <v>260</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="58">
         <v>261</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="58">
         <v>262</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="58">
         <v>263</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="58">
         <v>264</v>
       </c>
@@ -10541,7 +10541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="58">
         <v>265</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="58">
         <v>266</v>
       </c>
@@ -10593,7 +10593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="58">
         <v>267</v>
       </c>
@@ -10619,7 +10619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="58">
         <v>268</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="58">
         <v>269</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="58">
         <v>270</v>
       </c>
@@ -10697,7 +10697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="58">
         <v>271</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="58">
         <v>272</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="58">
         <v>273</v>
       </c>
@@ -10775,7 +10775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="58">
         <v>274</v>
       </c>
@@ -10801,7 +10801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="58">
         <v>275</v>
       </c>
@@ -10827,7 +10827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="58">
         <v>276</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="58">
         <v>277</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="58">
         <v>278</v>
       </c>
@@ -10905,7 +10905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="58">
         <v>279</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="58">
         <v>280</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="58">
         <v>281</v>
       </c>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="58">
         <v>282</v>
       </c>
@@ -11009,7 +11009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="58">
         <v>283</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="58">
         <v>284</v>
       </c>
@@ -11061,7 +11061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="58">
         <v>285</v>
       </c>
@@ -11087,7 +11087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="58">
         <v>286</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="58">
         <v>287</v>
       </c>
@@ -11139,10 +11139,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="58"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="59"/>
       <c r="B292" s="69"/>
       <c r="C292" s="66"/>
@@ -11150,7 +11150,7 @@
       <c r="G292" s="39"/>
       <c r="H292" s="40"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="60"/>
       <c r="B293" s="69"/>
       <c r="C293" s="67"/>
@@ -11158,7 +11158,7 @@
       <c r="G293" s="35"/>
       <c r="H293" s="6"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="61"/>
       <c r="B294" s="69"/>
       <c r="C294" s="67"/>
@@ -11166,7 +11166,7 @@
       <c r="G294" s="35"/>
       <c r="H294" s="6"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="62"/>
       <c r="B295" s="69"/>
       <c r="C295" s="67"/>
@@ -11174,7 +11174,7 @@
       <c r="G295" s="35"/>
       <c r="H295" s="6"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="62"/>
       <c r="B296" s="69"/>
       <c r="C296" s="67"/>
@@ -11182,7 +11182,7 @@
       <c r="G296" s="35"/>
       <c r="H296" s="6"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="62"/>
       <c r="B297" s="69"/>
       <c r="C297" s="67"/>
@@ -11190,7 +11190,7 @@
       <c r="G297" s="35"/>
       <c r="H297" s="6"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="60"/>
       <c r="B298" s="69"/>
       <c r="C298" s="67"/>
@@ -11198,7 +11198,7 @@
       <c r="G298" s="35"/>
       <c r="H298" s="6"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="61"/>
       <c r="B299" s="69"/>
       <c r="C299" s="67"/>
@@ -11206,7 +11206,7 @@
       <c r="G299" s="35"/>
       <c r="H299" s="6"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="62"/>
       <c r="B300" s="69"/>
       <c r="C300" s="67"/>
@@ -11214,7 +11214,7 @@
       <c r="G300" s="35"/>
       <c r="H300" s="6"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="62"/>
       <c r="B301" s="69"/>
       <c r="C301" s="67"/>
@@ -11222,7 +11222,7 @@
       <c r="G301" s="35"/>
       <c r="H301" s="6"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="62"/>
       <c r="B302" s="69"/>
       <c r="C302" s="67"/>
@@ -11230,7 +11230,7 @@
       <c r="G302" s="35"/>
       <c r="H302" s="6"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="60"/>
       <c r="B303" s="69"/>
       <c r="C303" s="67"/>
@@ -11238,7 +11238,7 @@
       <c r="G303" s="35"/>
       <c r="H303" s="6"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="61"/>
       <c r="B304" s="69"/>
       <c r="C304" s="67"/>
@@ -11246,7 +11246,7 @@
       <c r="G304" s="35"/>
       <c r="H304" s="6"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="62"/>
       <c r="B305" s="69"/>
       <c r="C305" s="67"/>
@@ -11254,7 +11254,7 @@
       <c r="G305" s="35"/>
       <c r="H305" s="6"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="62"/>
       <c r="B306" s="69"/>
       <c r="C306" s="67"/>
@@ -11262,7 +11262,7 @@
       <c r="G306" s="35"/>
       <c r="H306" s="6"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="62"/>
       <c r="B307" s="69"/>
       <c r="C307" s="67"/>
@@ -11270,7 +11270,7 @@
       <c r="G307" s="35"/>
       <c r="H307" s="6"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="60"/>
       <c r="B308" s="69"/>
       <c r="C308" s="67"/>
@@ -11278,7 +11278,7 @@
       <c r="G308" s="35"/>
       <c r="H308" s="6"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="61"/>
       <c r="B309" s="69"/>
       <c r="C309" s="67"/>
@@ -11286,7 +11286,7 @@
       <c r="G309" s="35"/>
       <c r="H309" s="6"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="62"/>
       <c r="B310" s="69"/>
       <c r="C310" s="67"/>
@@ -11294,7 +11294,7 @@
       <c r="G310" s="35"/>
       <c r="H310" s="6"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="62"/>
       <c r="B311" s="69"/>
       <c r="C311" s="67"/>
@@ -11302,7 +11302,7 @@
       <c r="G311" s="35"/>
       <c r="H311" s="6"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="62"/>
       <c r="B312" s="69"/>
       <c r="C312" s="67"/>
@@ -11310,7 +11310,7 @@
       <c r="G312" s="35"/>
       <c r="H312" s="6"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="60"/>
       <c r="B313" s="69"/>
       <c r="C313" s="67"/>
@@ -11318,7 +11318,7 @@
       <c r="G313" s="35"/>
       <c r="H313" s="6"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="61"/>
       <c r="B314" s="69"/>
       <c r="C314" s="67"/>
@@ -11326,7 +11326,7 @@
       <c r="G314" s="35"/>
       <c r="H314" s="6"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="62"/>
       <c r="B315" s="69"/>
       <c r="C315" s="67"/>
@@ -11334,7 +11334,7 @@
       <c r="G315" s="35"/>
       <c r="H315" s="6"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="62"/>
       <c r="B316" s="69"/>
       <c r="C316" s="67"/>
@@ -11342,7 +11342,7 @@
       <c r="G316" s="35"/>
       <c r="H316" s="6"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="62"/>
       <c r="B317" s="69"/>
       <c r="C317" s="67"/>
@@ -11350,7 +11350,7 @@
       <c r="G317" s="35"/>
       <c r="H317" s="6"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="60"/>
       <c r="B318" s="69"/>
       <c r="C318" s="67"/>
@@ -11358,7 +11358,7 @@
       <c r="G318" s="35"/>
       <c r="H318" s="6"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="61"/>
       <c r="B319" s="69"/>
       <c r="C319" s="67"/>
@@ -11366,7 +11366,7 @@
       <c r="G319" s="35"/>
       <c r="H319" s="6"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="62"/>
       <c r="B320" s="69"/>
       <c r="C320" s="67"/>
@@ -11374,7 +11374,7 @@
       <c r="G320" s="35"/>
       <c r="H320" s="6"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="62"/>
       <c r="B321" s="69"/>
       <c r="C321" s="67"/>
@@ -11382,7 +11382,7 @@
       <c r="G321" s="35"/>
       <c r="H321" s="6"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="62"/>
       <c r="B322" s="69"/>
       <c r="C322" s="67"/>
@@ -11390,7 +11390,7 @@
       <c r="G322" s="35"/>
       <c r="H322" s="6"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="60"/>
       <c r="B323" s="69"/>
       <c r="C323" s="67"/>
@@ -11398,7 +11398,7 @@
       <c r="G323" s="35"/>
       <c r="H323" s="6"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="61"/>
       <c r="B324" s="69"/>
       <c r="C324" s="67"/>
@@ -11406,7 +11406,7 @@
       <c r="G324" s="35"/>
       <c r="H324" s="6"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="62"/>
       <c r="B325" s="69"/>
       <c r="C325" s="67"/>
@@ -11414,7 +11414,7 @@
       <c r="G325" s="35"/>
       <c r="H325" s="6"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="62"/>
       <c r="B326" s="69"/>
       <c r="C326" s="67"/>
@@ -11422,7 +11422,7 @@
       <c r="G326" s="35"/>
       <c r="H326" s="6"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="62"/>
       <c r="B327" s="69"/>
       <c r="C327" s="67"/>
@@ -11430,7 +11430,7 @@
       <c r="G327" s="35"/>
       <c r="H327" s="6"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="60"/>
       <c r="B328" s="69"/>
       <c r="C328" s="67"/>
@@ -11438,7 +11438,7 @@
       <c r="G328" s="35"/>
       <c r="H328" s="6"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="61"/>
       <c r="B329" s="69"/>
       <c r="C329" s="67"/>
@@ -11446,7 +11446,7 @@
       <c r="G329" s="35"/>
       <c r="H329" s="6"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="62"/>
       <c r="B330" s="69"/>
       <c r="C330" s="67"/>
@@ -11454,7 +11454,7 @@
       <c r="G330" s="35"/>
       <c r="H330" s="6"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="62"/>
       <c r="B331" s="69"/>
       <c r="C331" s="67"/>
@@ -11462,7 +11462,7 @@
       <c r="G331" s="35"/>
       <c r="H331" s="6"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="62"/>
       <c r="B332" s="69"/>
       <c r="C332" s="67"/>
@@ -11470,7 +11470,7 @@
       <c r="G332" s="35"/>
       <c r="H332" s="6"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="60"/>
       <c r="B333" s="69"/>
       <c r="C333" s="67"/>
@@ -11478,7 +11478,7 @@
       <c r="G333" s="35"/>
       <c r="H333" s="6"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="61"/>
       <c r="B334" s="69"/>
       <c r="C334" s="67"/>
@@ -11486,7 +11486,7 @@
       <c r="G334" s="35"/>
       <c r="H334" s="6"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="62"/>
       <c r="B335" s="69"/>
       <c r="C335" s="67"/>
@@ -11494,7 +11494,7 @@
       <c r="G335" s="35"/>
       <c r="H335" s="6"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="62"/>
       <c r="B336" s="69"/>
       <c r="C336" s="67"/>
@@ -11502,7 +11502,7 @@
       <c r="G336" s="35"/>
       <c r="H336" s="6"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="62"/>
       <c r="B337" s="69"/>
       <c r="C337" s="67"/>
@@ -11510,7 +11510,7 @@
       <c r="G337" s="35"/>
       <c r="H337" s="6"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="60"/>
       <c r="B338" s="69"/>
       <c r="C338" s="67"/>
@@ -11518,7 +11518,7 @@
       <c r="G338" s="35"/>
       <c r="H338" s="6"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="61"/>
       <c r="B339" s="69"/>
       <c r="C339" s="67"/>
@@ -11526,7 +11526,7 @@
       <c r="G339" s="35"/>
       <c r="H339" s="6"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="62"/>
       <c r="B340" s="69"/>
       <c r="C340" s="67"/>
@@ -11534,7 +11534,7 @@
       <c r="G340" s="35"/>
       <c r="H340" s="6"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="62"/>
       <c r="B341" s="69"/>
       <c r="C341" s="67"/>
@@ -11542,7 +11542,7 @@
       <c r="G341" s="35"/>
       <c r="H341" s="6"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="62"/>
       <c r="B342" s="69"/>
       <c r="C342" s="67"/>
@@ -11550,7 +11550,7 @@
       <c r="G342" s="35"/>
       <c r="H342" s="6"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="60"/>
       <c r="B343" s="69"/>
       <c r="C343" s="67"/>
@@ -11558,7 +11558,7 @@
       <c r="G343" s="35"/>
       <c r="H343" s="6"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="61"/>
       <c r="B344" s="69"/>
       <c r="C344" s="67"/>
@@ -11566,7 +11566,7 @@
       <c r="G344" s="35"/>
       <c r="H344" s="6"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="62"/>
       <c r="B345" s="69"/>
       <c r="C345" s="67"/>
@@ -11574,7 +11574,7 @@
       <c r="G345" s="35"/>
       <c r="H345" s="6"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="62"/>
       <c r="B346" s="69"/>
       <c r="C346" s="67"/>
@@ -11594,14 +11594,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11612,7 +11612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -11623,7 +11623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>0</v>
       </c>

--- a/data/Escenarios_DCH/Carga_on_board_fixed_3estaciones/elmo_data.xlsx
+++ b/data/Escenarios_DCH/Carga_on_board_fixed_3estaciones/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH\Carga_on_board_fixed_3estaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698B6125-96A9-4479-822A-FF72E05FB9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E5CEF3-1094-43E0-8101-7118451B3CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -3449,7 +3449,7 @@
         <v>215756</v>
       </c>
       <c r="D3">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -3472,7 +3472,7 @@
         <v>215756</v>
       </c>
       <c r="D4">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3495,7 +3495,7 @@
         <v>215756</v>
       </c>
       <c r="D5">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>2</v>
